--- a/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/fossielaard/fossielaard.xlsx
+++ b/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/fossielaard/fossielaard.xlsx
@@ -762,7 +762,7 @@
         <v>be.vlaanderen.bodemenondergrond.data.id.conceptscheme.fossielaard</v>
       </c>
       <c r="D12" t="str">
-        <v>null</v>
+        <v>Indicatie van fossielaard.</v>
       </c>
       <c r="E12" t="str">
         <v>null</v>
@@ -771,10 +771,10 @@
         <v>null</v>
       </c>
       <c r="G12" t="str">
-        <v>null</v>
+        <v>Indicatie van fossielaard.</v>
       </c>
       <c r="H12" t="str">
-        <v>lijst met soorten fossielen</v>
+        <v>Codelijst fossielaard</v>
       </c>
       <c r="I12" t="str">
         <v>null</v>

--- a/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/fossielaard/fossielaard.xlsx
+++ b/src/main/resources/be/vlaanderen/bodemenondergrond/data/id/conceptscheme/fossielaard/fossielaard.xlsx
@@ -445,7 +445,7 @@
         <v>Fossiel van dierlijke oorsprong uit een brakwateromgeving (bv. estuarium).</v>
       </c>
       <c r="E2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F2" t="str">
         <v>brakwaterfauna</v>
@@ -457,7 +457,7 @@
         <v>brakwaterfauna</v>
       </c>
       <c r="I2" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J2" t="str">
         <v>null</v>
@@ -477,7 +477,7 @@
         <v>Sporenfossiel uit een brakwateromgeving.</v>
       </c>
       <c r="E3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F3" t="str">
         <v>brakwaterichnofossiel</v>
@@ -489,7 +489,7 @@
         <v>brakwaterichnofossiel</v>
       </c>
       <c r="I3" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J3" t="str">
         <v>null</v>
@@ -509,7 +509,7 @@
         <v>Fossiel van dierlijke oorsprong.</v>
       </c>
       <c r="E4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F4" t="str">
         <v>fauna</v>
@@ -521,7 +521,7 @@
         <v>fauna</v>
       </c>
       <c r="I4" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J4" t="str">
         <v>null</v>
@@ -541,7 +541,7 @@
         <v>Fossiel van plantaardige oorsprong.</v>
       </c>
       <c r="E5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F5" t="str">
         <v>flora</v>
@@ -553,7 +553,7 @@
         <v>flora</v>
       </c>
       <c r="I5" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J5" t="str">
         <v>null</v>
@@ -573,7 +573,7 @@
         <v>Sporenfossiel.</v>
       </c>
       <c r="E6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F6" t="str">
         <v>ichnofossiel</v>
@@ -585,7 +585,7 @@
         <v>ichnofossiel</v>
       </c>
       <c r="I6" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J6" t="str">
         <v>null</v>
@@ -605,7 +605,7 @@
         <v>Fossiel van dierlijke oorsprong uit een mariene omgeving.</v>
       </c>
       <c r="E7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F7" t="str">
         <v>marienefauna</v>
@@ -617,7 +617,7 @@
         <v>mariene fauna</v>
       </c>
       <c r="I7" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J7" t="str">
         <v>null</v>
@@ -637,7 +637,7 @@
         <v>Sporenfossiel uit een mariene omgeving.</v>
       </c>
       <c r="E8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F8" t="str">
         <v>marienichnofossiel</v>
@@ -649,7 +649,7 @@
         <v>marien ichnofossiel</v>
       </c>
       <c r="I8" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J8" t="str">
         <v>null</v>
@@ -669,7 +669,7 @@
         <v>Fossiel van onbepaalde oorsprong.</v>
       </c>
       <c r="E9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F9" t="str">
         <v>onbepaald</v>
@@ -681,7 +681,7 @@
         <v>onbepaald</v>
       </c>
       <c r="I9" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J9" t="str">
         <v>null</v>
@@ -701,7 +701,7 @@
         <v>Fossiel van dierlijke oorsprong uit een zoetwateromgeving.</v>
       </c>
       <c r="E10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F10" t="str">
         <v>zoetwaterfauna</v>
@@ -713,7 +713,7 @@
         <v>zoetwaterfauna</v>
       </c>
       <c r="I10" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J10" t="str">
         <v>null</v>
@@ -733,7 +733,7 @@
         <v>Sporenfossiel uit een zoetwateromgeving.</v>
       </c>
       <c r="E11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="F11" t="str">
         <v>zoetwaterichnofossiel</v>
@@ -745,7 +745,7 @@
         <v>zoetwaterichnofossiel</v>
       </c>
       <c r="I11" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="J11" t="str">
         <v>null</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>https://data.omgeving.vlaanderen.be/id/conceptscheme/fossielaard</v>
+        <v>https://data.bodemenondergrond.vlaanderen.be/id/conceptscheme/fossielaard</v>
       </c>
       <c r="B12" t="str">
         <v>http://www.w3.org/2004/02/skos/core#ConceptScheme</v>
